--- a/data/trans_orig/P25C_R_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P25C_R_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si dejó de fumar con o sin ayuda específica en 2023</t>
+          <t>Población según si dejó de fumar con o sin ayuda específica en 2023 (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1743</t>
+          <t>2044</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11811</t>
+          <t>10635</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3318</t>
+          <t>3498</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11802</t>
+          <t>11364</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6558</t>
+          <t>6556</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18418</t>
+          <t>18605</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,87%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>111567</t>
+          <t>112743</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>121635</t>
+          <t>121334</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53229</t>
+          <t>53667</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61713</t>
+          <t>61533</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>169990</t>
+          <t>169803</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>181850</t>
+          <t>181852</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1866</t>
+          <t>1818</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10972</t>
+          <t>10817</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1778</t>
+          <t>1538</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8200</t>
+          <t>7438</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4841</t>
+          <t>4859</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16218</t>
+          <t>15870</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,58%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>82314</t>
+          <t>82469</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>91420</t>
+          <t>91468</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>48521</t>
+          <t>49283</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>54943</t>
+          <t>55183</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>133789</t>
+          <t>134137</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>145166</t>
+          <t>145148</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,76%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>561</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25130</t>
+          <t>25743</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>4362</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26014</t>
+          <t>25955</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>314396</t>
+          <t>313783</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>338789</t>
+          <t>338965</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17720</t>
+          <t>17446</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>335321</t>
+          <t>335380</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>361046</t>
+          <t>360273</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>99,71%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9981</t>
+          <t>9789</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24412</t>
+          <t>24432</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2996</t>
+          <t>3140</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>11300</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15028</t>
+          <t>14995</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31918</t>
+          <t>31479</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,73%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>164863</t>
+          <t>164843</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>179294</t>
+          <t>179486</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>67996</t>
+          <t>67677</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>75981</t>
+          <t>75837</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>236335</t>
+          <t>236774</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>253225</t>
+          <t>253258</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,41%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4932</t>
+          <t>5092</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16293</t>
+          <t>16939</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5557</t>
+          <t>5561</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14321</t>
+          <t>14562</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12574</t>
+          <t>12339</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27492</t>
+          <t>26878</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>16,99%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>71786</t>
+          <t>71140</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>83147</t>
+          <t>82987</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>55795</t>
+          <t>55554</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>64559</t>
+          <t>64555</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>130703</t>
+          <t>131317</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>145621</t>
+          <t>145856</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>92,2%</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4951</t>
+          <t>5163</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3795</t>
+          <t>3904</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>700</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6900</t>
+          <t>7093</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>16,04%</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1818</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>33459</t>
+          <t>33350</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>37332</t>
+          <t>37139</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>43540</t>
+          <t>43532</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,42%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19445</t>
+          <t>15216</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>68542</t>
+          <t>66176</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21703</t>
+          <t>21366</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>37735</t>
+          <t>37026</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>35962</t>
+          <t>37300</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>95853</t>
+          <t>98011</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>771981</t>
+          <t>774347</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>821078</t>
+          <t>825307</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>292173</t>
+          <t>292882</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>308205</t>
+          <t>308542</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1074577</t>
+          <t>1072419</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1134468</t>
+          <t>1133130</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,81%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P25C_R_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P25C_R_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4876</t>
+          <t>5179</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2044</t>
+          <t>1953</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10635</t>
+          <t>10515</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6574</t>
+          <t>6767</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3498</t>
+          <t>3527</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11364</t>
+          <t>11680</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>11450</t>
+          <t>11947</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6556</t>
+          <t>6727</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18605</t>
+          <t>18306</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,15%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>118502</t>
+          <t>125441</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>112743</t>
+          <t>120105</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>121334</t>
+          <t>128667</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>58457</t>
+          <t>62658</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53667</t>
+          <t>57745</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61533</t>
+          <t>65898</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>176958</t>
+          <t>188097</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>169803</t>
+          <t>181738</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>181852</t>
+          <t>193317</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,64%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>123378</t>
+          <t>130620</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>123378</t>
+          <t>130620</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>123378</t>
+          <t>130620</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>65031</t>
+          <t>69425</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>65031</t>
+          <t>69425</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>65031</t>
+          <t>69425</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>188408</t>
+          <t>200044</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>188408</t>
+          <t>200044</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>188408</t>
+          <t>200044</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5193</t>
+          <t>6320</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1818</t>
+          <t>2165</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10817</t>
+          <t>13509</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3897</t>
+          <t>4778</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1538</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7438</t>
+          <t>9148</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>9090</t>
+          <t>11098</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4859</t>
+          <t>6119</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15870</t>
+          <t>19046</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>11,53%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>88093</t>
+          <t>96031</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>82469</t>
+          <t>88842</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>91468</t>
+          <t>100186</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>52824</t>
+          <t>58058</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>49283</t>
+          <t>53688</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>55183</t>
+          <t>60807</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>140917</t>
+          <t>154090</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>134137</t>
+          <t>146142</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>145148</t>
+          <t>159069</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,3%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>93286</t>
+          <t>102351</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>93286</t>
+          <t>102351</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>93286</t>
+          <t>102351</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>56721</t>
+          <t>62836</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>56721</t>
+          <t>62836</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>56721</t>
+          <t>62836</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>150007</t>
+          <t>165188</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>150007</t>
+          <t>165188</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>150007</t>
+          <t>165188</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5840</t>
+          <t>6903</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>3358</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25743</t>
+          <t>13119</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1341</t>
+          <t>1446</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1456,12 +1456,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4362</t>
+          <t>4840</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>7180</t>
+          <t>8348</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1062</t>
+          <t>4259</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25955</t>
+          <t>14731</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>11,54%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>333686</t>
+          <t>98094</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>313783</t>
+          <t>91878</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>338965</t>
+          <t>101639</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,27 +1559,27 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20467</t>
+          <t>21236</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17446</t>
+          <t>17842</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21808</t>
+          <t>22682</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>354155</t>
+          <t>119331</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>335380</t>
+          <t>112948</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>360273</t>
+          <t>123420</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>96,66%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>339526</t>
+          <t>104997</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>339526</t>
+          <t>104997</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>339526</t>
+          <t>104997</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>21808</t>
+          <t>22682</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>21808</t>
+          <t>22682</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21808</t>
+          <t>22682</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>361335</t>
+          <t>127679</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>361335</t>
+          <t>127679</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>361335</t>
+          <t>127679</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15944</t>
+          <t>18273</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9789</t>
+          <t>11660</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24432</t>
+          <t>28496</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6267</t>
+          <t>6702</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3140</t>
+          <t>3210</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11300</t>
+          <t>12086</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>22211</t>
+          <t>24975</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14995</t>
+          <t>16877</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31479</t>
+          <t>34959</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,81%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>173331</t>
+          <t>192650</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>164843</t>
+          <t>182427</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>179486</t>
+          <t>199263</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>72710</t>
+          <t>78409</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>67677</t>
+          <t>73025</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>75837</t>
+          <t>81901</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>246042</t>
+          <t>271059</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>236774</t>
+          <t>261075</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>253258</t>
+          <t>279157</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,3%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>189275</t>
+          <t>210923</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>189275</t>
+          <t>210923</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>189275</t>
+          <t>210923</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>78977</t>
+          <t>85111</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>78977</t>
+          <t>85111</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>78977</t>
+          <t>85111</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>268253</t>
+          <t>296034</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>268253</t>
+          <t>296034</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>268253</t>
+          <t>296034</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>9695</t>
+          <t>10136</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5092</t>
+          <t>5583</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16939</t>
+          <t>16947</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>9306</t>
+          <t>9731</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5561</t>
+          <t>5856</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14562</t>
+          <t>15323</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>19001</t>
+          <t>19867</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12339</t>
+          <t>13439</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26878</t>
+          <t>28267</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,24%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>78384</t>
+          <t>84102</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>71140</t>
+          <t>77291</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>82987</t>
+          <t>88655</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>60810</t>
+          <t>70084</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>55554</t>
+          <t>64492</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>64555</t>
+          <t>73959</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>139194</t>
+          <t>154186</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>131317</t>
+          <t>145786</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>145856</t>
+          <t>160614</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,28%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>88079</t>
+          <t>94238</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>88079</t>
+          <t>94238</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>88079</t>
+          <t>94238</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>70116</t>
+          <t>79815</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>70116</t>
+          <t>79815</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>70116</t>
+          <t>79815</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>158195</t>
+          <t>174053</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>158195</t>
+          <t>174053</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>158195</t>
+          <t>174053</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1518</t>
+          <t>1433</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5163</t>
+          <t>4765</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>1174</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3904</t>
+          <t>4038</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2669</t>
+          <t>2608</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>897</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7093</t>
+          <t>6958</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,52%</t>
         </is>
       </c>
     </row>
@@ -2553,27 +2553,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>5460</t>
+          <t>5233</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1818</t>
+          <t>1901</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6978</t>
+          <t>6666</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2588,27 +2588,27 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>36103</t>
+          <t>36993</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>33350</t>
+          <t>34129</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>37254</t>
+          <t>38167</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>41563</t>
+          <t>42225</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>37139</t>
+          <t>37875</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>43532</t>
+          <t>43936</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,0%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6978</t>
+          <t>6666</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6978</t>
+          <t>6666</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6978</t>
+          <t>6666</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>37254</t>
+          <t>38167</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>37254</t>
+          <t>38167</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>37254</t>
+          <t>38167</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>44232</t>
+          <t>44833</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>44232</t>
+          <t>44833</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>44232</t>
+          <t>44833</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>43065</t>
+          <t>48244</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15216</t>
+          <t>36793</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>66176</t>
+          <t>62844</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>28536</t>
+          <t>30599</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21366</t>
+          <t>21788</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>37026</t>
+          <t>40549</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>71601</t>
+          <t>78843</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>37300</t>
+          <t>64076</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>98011</t>
+          <t>93943</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>9,32%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>797458</t>
+          <t>601552</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>774347</t>
+          <t>586952</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>825307</t>
+          <t>613003</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>301372</t>
+          <t>327437</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>292882</t>
+          <t>317487</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>308542</t>
+          <t>336248</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1098829</t>
+          <t>928988</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1072419</t>
+          <t>913888</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1133130</t>
+          <t>943755</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>93,64%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>840523</t>
+          <t>649796</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>840523</t>
+          <t>649796</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>840523</t>
+          <t>649796</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>329908</t>
+          <t>358036</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>329908</t>
+          <t>358036</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>329908</t>
+          <t>358036</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1170430</t>
+          <t>1007831</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1170430</t>
+          <t>1007831</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1170430</t>
+          <t>1007831</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
